--- a/excel/20260805_タイムレコード_00_定義表.xlsx
+++ b/excel/20260805_タイムレコード_00_定義表.xlsx
@@ -481,6 +481,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -583,6 +584,7 @@
         </is>
       </c>
     </row>
+    <row r="10"/>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
@@ -699,6 +701,7 @@
         </is>
       </c>
     </row>
+    <row r="18"/>
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
@@ -731,7 +734,7 @@
         </is>
       </c>
       <c r="B21" s="5" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
@@ -763,7 +766,7 @@
         </is>
       </c>
       <c r="B23" s="5" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
@@ -788,6 +791,7 @@
       </c>
       <c r="D24" s="5" t="inlineStr"/>
     </row>
+    <row r="25"/>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
@@ -925,6 +929,7 @@
       </c>
       <c r="D34" s="5" t="inlineStr"/>
     </row>
+    <row r="35"/>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
@@ -1174,6 +1179,7 @@
       </c>
       <c r="D51" s="5" t="inlineStr"/>
     </row>
+    <row r="52"/>
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
